--- a/out/Attention_Base_repeat_4_000007.xlsx
+++ b/out/Attention_Base_repeat_4_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>10.67907012395075</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>11.27907012395075</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.1214785345699065</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.1214785345699065</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.350885619758629e-05</v>
+        <v>-1.318189886200707e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.7321632397323752</v>
+        <v>0.1519677498049217</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.46545842325624</v>
+        <v>0.3041705658810579</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1097911438137972</v>
+        <v>0.02278824197728093</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9518947012812844</v>
+        <v>0.1975752323138914</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1372747102358227</v>
+        <v>0.02849277402667519</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.116670368164936</v>
+        <v>0.2317761119482045</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1967826461112384</v>
+        <v>0.04084409376813929</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.373038420346467</v>
+        <v>0.2849879307953839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2105184526747808</v>
+        <v>0.04369543800247998</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.597307351345162</v>
+        <v>0.3315374329688335</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2231063901292494</v>
+        <v>0.04630835705919324</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.833019085469454</v>
+        <v>0.3804620155180821</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1006837643598522</v>
+        <v>0.02089743439943389</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.811094679552205</v>
+        <v>0.3759113779325399</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04862565627917254</v>
+        <v>0.01009056890629882</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.807583232453053</v>
+        <v>0.3751805861922118</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02316867753908389</v>
+        <v>0.004805238747659061</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.805256255114777</v>
+        <v>0.3746940222774623</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006862180623952113</v>
+        <v>0.001420606643127081</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.795788932819602</v>
+        <v>0.3727246718020488</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004536897260261469</v>
+        <v>0.0009379843835590479</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.797998640916994</v>
+        <v>0.373179438613886</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002320085942499</v>
+        <v>0.0004771380075431698</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.798098252506395</v>
+        <v>0.373196153975697</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00118386798434055</v>
+        <v>0.0002416322236777603</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.79814552668101</v>
+        <v>0.3732020163398685</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004423189860551449</v>
+        <v>8.809684481350731e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.79784438854966</v>
+        <v>0.3731353835308058</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002383767632912877</v>
+        <v>4.532536461277475e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.797879399410737</v>
+        <v>0.3731387110630267</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001126200326826326</v>
+        <v>1.963662846730818e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.797865283292404</v>
+        <v>0.3731318016058083</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.781267869019299e-05</v>
+        <v>9.759326761525608e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.797888233616753</v>
+        <v>0.373132656664605</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.308665882696171e-05</v>
+        <v>3.234953259883613e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.797886551950965</v>
+        <v>0.3731283741422726</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.29836763541332e-05</v>
+        <v>-1.003627476859289e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.797880408501921</v>
+        <v>0.3731231267785742</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>-2.441707244474577e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.797880721933198</v>
+        <v>0.3731192452322545</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.280563881834207e-07</v>
+        <v>-3.834388722363316e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.797874578137222</v>
+        <v>0.3731140164730593</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.797868893603194</v>
+        <v>0.3731138800672523</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.79786414232798</v>
+        <v>0.3731139634263567</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.797858853180418</v>
+        <v>0.3731138194424491</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.797858830446117</v>
+        <v>0.3731137967081478</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.797859148726333</v>
+        <v>0.3731141149883645</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.797860239972791</v>
+        <v>0.3731152062348214</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.797859550365655</v>
+        <v>0.3731145166276854</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.797859580678056</v>
+        <v>0.3731145469400871</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.797859391225546</v>
+        <v>0.373114357487577</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.797859444272249</v>
+        <v>0.3731144105342799</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.797859497318952</v>
+        <v>0.3731144635809828</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.79785945942845</v>
+        <v>0.3731144256904808</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.797859330600743</v>
+        <v>0.3731142968627741</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.797859186616836</v>
+        <v>0.3731141528788665</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.797859027476727</v>
+        <v>0.3731139937387581</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.79785908052343</v>
+        <v>0.373114046785461</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.797859027476727</v>
+        <v>0.3731139937387581</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.797859027476727</v>
+        <v>0.3731139937387581</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.797858845602318</v>
+        <v>0.3731138118643486</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.797859012320526</v>
+        <v>0.3731139785825573</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.797859209351137</v>
+        <v>0.3731141756131677</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.797859050211029</v>
+        <v>0.3731140164730593</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.79785908810153</v>
+        <v>0.3731140543635613</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.797859285132141</v>
+        <v>0.3731142513941715</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.79785926239784</v>
+        <v>0.3731142286598703</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.797859110835832</v>
+        <v>0.3731140770978625</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.797859035054828</v>
+        <v>0.3731140013168585</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.797859133570133</v>
+        <v>0.3731140998321636</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.797859141148233</v>
+        <v>0.373114107410264</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.797859406381747</v>
+        <v>0.3731143726437779</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.797859110835832</v>
+        <v>0.3731140770978625</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.797859353335044</v>
+        <v>0.3731143195970753</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.797859436694148</v>
+        <v>0.3731144029561796</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.79785926997594</v>
+        <v>0.3731142362379709</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.79785945942845</v>
+        <v>0.3731144256904808</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.797859110835832</v>
+        <v>0.3731140770978625</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.797858906227121</v>
+        <v>0.3731138724891518</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.797859019898627</v>
+        <v>0.3731139861606578</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.797859035054828</v>
+        <v>0.3731140013168585</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.797858800133715</v>
+        <v>0.3731137663957463</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.797858860758518</v>
+        <v>0.3731138270205495</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.797858731930812</v>
+        <v>0.3731136981928428</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.797858868336619</v>
+        <v>0.3731138345986498</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.797859042632928</v>
+        <v>0.373114008894959</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.797859186616836</v>
+        <v>0.3731141528788665</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.797859019898627</v>
+        <v>0.3731139861606578</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.797859012320526</v>
+        <v>0.3731139785825573</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.797858724352711</v>
+        <v>0.3731136906147422</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.797858739508913</v>
+        <v>0.3731137057709431</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.797858966851924</v>
+        <v>0.373113933113955</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.797858951695724</v>
+        <v>0.3731139179577541</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.797859057789129</v>
+        <v>0.3731140240511596</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.797858784977515</v>
+        <v>0.3731137512395454</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.79785888349282</v>
+        <v>0.3731138497548506</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.797859035054828</v>
+        <v>0.3731140013168585</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.797859050211029</v>
+        <v>0.3731140164730593</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.797859027476727</v>
+        <v>0.3731139937387581</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.797859110835832</v>
+        <v>0.3731140770978625</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4785214654300935</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.797859209351137</v>
+        <v>0.3731141756131677</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.797859042632928</v>
+        <v>0.373114008894959</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.797859027476727</v>
+        <v>0.3731139937387581</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.797858997164326</v>
+        <v>0.3731139634263567</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.797858982008125</v>
+        <v>0.3731139482701558</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.797859019898627</v>
+        <v>0.3731139861606578</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.797859035054828</v>
+        <v>0.3731140013168585</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.797859027476727</v>
+        <v>0.3731139937387581</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_4_000007.xlsx
+++ b/out/Attention_Base_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>10.67907012395075</v>
+        <v>1.338792640423968</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.4785214654300935</v>
+        <v>1.839195093615979</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>11.27907012395075</v>
+        <v>1.038390187231957</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.1214785345699065</v>
+        <v>1.038390187231957</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.1214785345699065</v>
+        <v>0.0375852808479359</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4785214654300935</v>
+        <v>0.0375852808479359</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC39" t="n">
-        <v>-6.350885619758629e-05</v>
+        <v>-8.76145628024824e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>0.7321632397323752</v>
+        <v>1.010066510700142</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC40" t="n">
-        <v>1.46545842325624</v>
+        <v>2.02169440194039</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1097911438137972</v>
+        <v>0.1514639789595488</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC41" t="n">
-        <v>0.9518947012812844</v>
+        <v>1.313200200967344</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1372747102358227</v>
+        <v>0.1893792001503588</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.116670368164936</v>
+        <v>1.540518789421072</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.1967826461112384</v>
+        <v>0.2714741853033066</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.373038420346467</v>
+        <v>1.89419504712886</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2105184526747808</v>
+        <v>0.2904239527861504</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC44" t="n">
-        <v>1.597307351345162</v>
+        <v>2.203588682699544</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2231063901292494</v>
+        <v>0.3077908522944665</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.833019085469454</v>
+        <v>2.528768410879833</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1006837643598522</v>
+        <v>0.1389002871077845</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.811094679552205</v>
+        <v>2.498522359825531</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.04862565627917254</v>
+        <v>0.06708184685886588</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC47" t="n">
-        <v>1.807583232453053</v>
+        <v>2.493678136931575</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02316867753908389</v>
+        <v>0.0319625028745364</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.805256255114777</v>
+        <v>2.490467962910455</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006862180623952113</v>
+        <v>0.009468526714113601</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.795788932819602</v>
+        <v>2.477409343390351</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004536897260261469</v>
+        <v>0.006261376347014713</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.797998640916994</v>
+        <v>2.480459613366261</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002320085942499</v>
+        <v>0.003201709727720796</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.798098252506395</v>
+        <v>2.480598914208837</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.00118386798434055</v>
+        <v>0.001635859284060201</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.79814552668101</v>
+        <v>2.480666030930016</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004423189860551449</v>
+        <v>0.0006118612075041338</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.79784438854966</v>
+        <v>2.480252650935008</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002383767632912877</v>
+        <v>0.0003307774327442512</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.797879399410737</v>
+        <v>2.480302826466306</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001126200326826326</v>
+        <v>0.000157124909913899</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.797865283292404</v>
+        <v>2.480285261005901</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.781267869019299e-05</v>
+        <v>9.536342197837412e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.797888233616753</v>
+        <v>2.480318787128652</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.308665882696171e-05</v>
+        <v>4.749782703175804e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.797886551950965</v>
+        <v>2.480318361048782</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.29836763541332e-05</v>
+        <v>1.997732826962944e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.797880408501921</v>
+        <v>2.480311784713266</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>6.512317399864405e-06</v>
+        <v>1.162890291091525e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.797880721933198</v>
+        <v>2.480314054662188</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>8.280563881834207e-07</v>
+        <v>1.993667665820105e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.797874578137222</v>
+        <v>2.480307568435511</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-2.941261685029097e-06</v>
+        <v>-1.911892527543644e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.797868893603194</v>
+        <v>2.480301609837373</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-3.887371769088796e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.79786414232798</v>
+        <v>2.480296940568736</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.797858853180418</v>
+        <v>2.480291651421174</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.797858830446117</v>
+        <v>2.480291628686873</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.797859148726333</v>
+        <v>2.480291946967089</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.797860239972791</v>
+        <v>2.480293038213546</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.797859550365655</v>
+        <v>2.48029234860641</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.797859580678056</v>
+        <v>2.480292378918812</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.797859391225546</v>
+        <v>2.480292189466302</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.797859444272249</v>
+        <v>2.480292242513005</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.797859497318952</v>
+        <v>2.480292295559708</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.79785945942845</v>
+        <v>2.480292257669205</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.797859330600743</v>
+        <v>2.480292128841499</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.797859186616836</v>
+        <v>2.480291984857591</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.79785908052343</v>
+        <v>2.480291878764186</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.797858845602318</v>
+        <v>2.480291643843073</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.797859012320526</v>
+        <v>2.480291810561282</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.797859209351137</v>
+        <v>2.480292007591892</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.797859050211029</v>
+        <v>2.480291848451784</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.79785908810153</v>
+        <v>2.480291886342286</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.797859285132141</v>
+        <v>2.480292083372897</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.79785926239784</v>
+        <v>2.480292060638595</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.797859110835832</v>
+        <v>2.480291909076587</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.797859035054828</v>
+        <v>2.480291833295583</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.797859133570133</v>
+        <v>2.480291931810888</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.797859141148233</v>
+        <v>2.480291939388989</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.797859406381747</v>
+        <v>2.480292204622503</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.797859110835832</v>
+        <v>2.480291909076587</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.797859353335044</v>
+        <v>2.4802921515758</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.797859436694148</v>
+        <v>2.480292234934904</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.79785926997594</v>
+        <v>2.480292068216695</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.79785945942845</v>
+        <v>2.480292257669205</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.797859110835832</v>
+        <v>2.480291909076587</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.797858906227121</v>
+        <v>2.480291704467877</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.797859019898627</v>
+        <v>2.480291818139383</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.797859035054828</v>
+        <v>2.480291833295583</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.797858800133715</v>
+        <v>2.480291598374471</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.797858860758518</v>
+        <v>2.480291658999274</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.797858731930812</v>
+        <v>2.480291530171568</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.797858868336619</v>
+        <v>2.480291666577374</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.797859042632928</v>
+        <v>2.480291840873684</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.797859186616836</v>
+        <v>2.480291984857591</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.797859019898627</v>
+        <v>2.480291818139383</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.797859012320526</v>
+        <v>2.480291810561282</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.797858724352711</v>
+        <v>2.480291522593467</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.797858739508913</v>
+        <v>2.480291537749668</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.797858966851924</v>
+        <v>2.48029176509268</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.797858951695724</v>
+        <v>2.480291749936479</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.797859057789129</v>
+        <v>2.480291856029885</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.797858784977515</v>
+        <v>2.48029158321827</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.79785888349282</v>
+        <v>2.480291681733576</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.797859035054828</v>
+        <v>2.480291833295583</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.797859050211029</v>
+        <v>2.480291848451784</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.797859110835832</v>
+        <v>2.480291909076587</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.797859209351137</v>
+        <v>2.480292007591892</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.797859042632928</v>
+        <v>2.480291840873684</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.797858997164326</v>
+        <v>2.480291795405082</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.797858982008125</v>
+        <v>2.48029178024888</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.797859019898627</v>
+        <v>2.480291818139383</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.797859035054828</v>
+        <v>2.480291833295583</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4785214654300935</v>
+        <v>-0.1624147191520641</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.797859027476727</v>
+        <v>2.480291825717483</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention_Base_repeat_4_000007.xlsx
+++ b/out/Attention_Base_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>5.831988528370857e-05</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.338792640423968</v>
+        <v>-0.16</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.00018726522102952</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.839195093615979</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.0001857155002653599</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.038390187231957</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.002958708442747593</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.038390187231957</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.004392537288367748</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.0375852808479359</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.004084950778633356</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.0375852808479359</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.003417308907955885</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003091124817728996</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.002721499186009169</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.002461718395352364</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.002172800712287426</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001889037434011698</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.001770273316651583</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.001674511004239321</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.001632334664463997</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.00155196338891983</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.00150321563705802</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.001394461840391159</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.001425502356141806</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.001444181893020868</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.001540721394121647</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.001854562200605869</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.00200771214440465</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.002028199378401041</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.00199555279687047</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.001921168994158506</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.001821978483349085</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.001817905344069004</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.001753123011440039</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.001725474372506142</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.001612789463251829</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.001556174363940954</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.001506079453974962</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.001476575154811144</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.001644146163016558</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.002613350749015808</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.003319945652037859</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.003784591797739267</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-8.76145628024824e-05</v>
+        <v>-2.374188724905252e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.010066510700142</v>
+        <v>0.2737088198054883</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.004246323369443417</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.02169440194039</v>
+        <v>0.5478408956059538</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1514639789595488</v>
+        <v>0.04104385848346254</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.004634206183254719</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.313200200967344</v>
+        <v>0.3558523317891599</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.1893792001503588</v>
+        <v>0.05131817791221478</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.004855391569435596</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.540518789421072</v>
+        <v>0.4174514153839927</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.2714741853033066</v>
+        <v>0.07356452734066871</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.005364302545785904</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>1.89419504712886</v>
+        <v>0.5132911398550274</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.2904239527861504</v>
+        <v>0.07869912454886685</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.006159749813377857</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.203588682699544</v>
+        <v>0.5971310431035201</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3077908522944665</v>
+        <v>0.08340520947857311</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.007064282894134521</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.528768410879833</v>
+        <v>0.6852490732180814</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1389002871077845</v>
+        <v>0.03763988566566401</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.008309738710522652</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.498522359825531</v>
+        <v>0.6770528489537041</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.06708184685886588</v>
+        <v>0.01817834438752623</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.009984487667679787</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.493678136931575</v>
+        <v>0.675740137249484</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0319625028745364</v>
+        <v>0.008659070097109081</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01076728105545044</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.490467962910455</v>
+        <v>0.6748678667302993</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009468526714113601</v>
+        <v>0.002562109210075422</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0119967358186841</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.477409343390351</v>
+        <v>0.6713256341973552</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006261376347014713</v>
+        <v>0.001692564140025768</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01214835699647665</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.480459613366261</v>
+        <v>0.6721485431140889</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003201709727720796</v>
+        <v>0.0008638323686951406</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01259809918701649</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.480598914208837</v>
+        <v>0.6721826568485764</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001635859284060201</v>
+        <v>0.0004399446647574287</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0126513410359621</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.480666030930016</v>
+        <v>0.6721972124257304</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0006118612075041338</v>
+        <v>0.00016227156669744</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01300928555428982</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.480252650935008</v>
+        <v>0.6720814738013171</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003307774327442512</v>
+        <v>8.575065749844627e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01313196681439877</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.480302826466306</v>
+        <v>0.6720914358767597</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000157124909913899</v>
+        <v>3.871014728070806e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.01315797306597233</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.480285261005901</v>
+        <v>0.6720830178176805</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.536342197837412e-05</v>
+        <v>2.255074328818113e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01307093631476164</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.480318787128652</v>
+        <v>0.6720885936160828</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.749782703175804e-05</v>
+        <v>9.411168204796322e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01317648962140083</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.480318361048782</v>
+        <v>0.6720848492020007</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.997732826962944e-05</v>
+        <v>1.993651915496244e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01276430860161781</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.480311784713266</v>
+        <v>0.6720794163155286</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.162890291091525e-05</v>
+        <v>-1.162560866711865e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.01403655484318733</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.480314054662188</v>
+        <v>0.6720763743857638</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.993667665820105e-06</v>
+        <v>-2.668777444726632e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01512918807566166</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.480307568435511</v>
+        <v>0.6720709168673735</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-1.911892527543644e-06</v>
+        <v>-3.970630842514548e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.01535086520016193</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.480301609837373</v>
+        <v>0.6720656428032632</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01544070243835449</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.480296940568736</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01570494845509529</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.480291651421174</v>
+        <v>0.67206558217846</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01561818271875381</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.480291628686873</v>
+        <v>0.6720655594441586</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01522206515073776</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.480291946967089</v>
+        <v>0.6720658777243753</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01332441903650761</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.480293038213546</v>
+        <v>0.6720669689708322</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01626784354448318</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.48029234860641</v>
+        <v>0.6720662793636962</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01891826465725899</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.480292378918812</v>
+        <v>0.6720663096760979</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.02035094238817692</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.480292189466302</v>
+        <v>0.6720661202235878</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.02101524360477924</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.480292242513005</v>
+        <v>0.6720661732702907</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.02195732295513153</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.480292295559708</v>
+        <v>0.6720662263169936</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.02223064750432968</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.480292257669205</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.02229752577841282</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.480292128841499</v>
+        <v>0.6720660595987848</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02261650934815407</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.480291984857591</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02288075536489487</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.480291825717483</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02272415533661842</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.480291878764186</v>
+        <v>0.6720658095214719</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.02313854917883873</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.480291825717483</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.02274990268051624</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.480291825717483</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.02246620878577232</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.480291643843073</v>
+        <v>0.6720655746003594</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.02200182341039181</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.480291810561282</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.02243931777775288</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.480292007591892</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.02274227514863014</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.480291848451784</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.02190795540809631</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.480291886342286</v>
+        <v>0.6720658170995721</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.02149126678705215</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.480292083372897</v>
+        <v>0.6720660141301823</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.02212902158498764</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.480292060638595</v>
+        <v>0.6720659913958812</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.02257693745195866</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.480291909076587</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.02246100641787052</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.480291833295583</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.02214189618825912</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.480291931810888</v>
+        <v>0.6720658625681745</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.02157844230532646</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.480291939388989</v>
+        <v>0.6720658701462748</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.0216869805008173</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.480292204622503</v>
+        <v>0.6720661353797887</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02216067165136337</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.480291909076587</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02147434279322624</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.4802921515758</v>
+        <v>0.6720660823330861</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02194270491600037</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.480292234934904</v>
+        <v>0.6720661656921904</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02102228254079819</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.480292068216695</v>
+        <v>0.6720659989739817</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02199344523251057</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.480292257669205</v>
+        <v>0.6720661884264916</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02296958304941654</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.480291909076587</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.02360677719116211</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.480291704467877</v>
+        <v>0.6720656352251626</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.02341977879405022</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.480291818139383</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.02309765852987766</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.480291833295583</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02332532964646816</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.480291598374471</v>
+        <v>0.6720655291317571</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.02339568734169006</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1624147191520641</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.480291658999274</v>
+        <v>0.6720655897565603</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.02334263175725937</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.480291530171568</v>
+        <v>0.6720654609288536</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.02200216241180897</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.480291666577374</v>
+        <v>0.6720655973346605</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.02241622656583786</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.480291840873684</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.02238054201006889</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.480291984857591</v>
+        <v>0.6720659156148774</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02223107777535915</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.480291818139383</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02236919663846493</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.480291810561282</v>
+        <v>0.6720657413185681</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.02289155125617981</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.480291522593467</v>
+        <v>0.6720654533507531</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.02250997349619865</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.480291537749668</v>
+        <v>0.6720654685069539</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.02208862453699112</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.48029176509268</v>
+        <v>0.6720656958499658</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.02156853675842285</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.480291749936479</v>
+        <v>0.6720656806937649</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.02175948768854141</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.480291856029885</v>
+        <v>0.6720657867871704</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.02187125384807587</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.48029158321827</v>
+        <v>0.6720655139755563</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.02137242816388607</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.480291681733576</v>
+        <v>0.6720656124908615</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.0210124459117651</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.480291833295583</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.02085329405963421</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.480291848451784</v>
+        <v>0.6720657792090702</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.02061165682971478</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.480291825717483</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.02028853818774223</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.480291909076587</v>
+        <v>0.6720658398338734</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.02038790658116341</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.480292007591892</v>
+        <v>0.6720659383491785</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02043489553034306</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.480291840873684</v>
+        <v>0.6720657716309698</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02025014534592628</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.480291825717483</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.02008612640202045</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.480291795405082</v>
+        <v>0.6720657261623675</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01992397010326385</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.48029178024888</v>
+        <v>0.6720657110061666</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01985200308263302</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.480291818139383</v>
+        <v>0.6720657488966687</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.01952400058507919</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.480291833295583</v>
+        <v>0.6720657640528693</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01925713568925858</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1624147191520641</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.480291825717483</v>
+        <v>0.672065756474769</v>
       </c>
     </row>
   </sheetData>
